--- a/Output/CVs_Info_Extracted.xlsx
+++ b/Output/CVs_Info_Extracted.xlsx
@@ -1,123 +1,37 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26327"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/88c389660cadc610/Desktop/Work/ResumeGPT/Output/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="11_2BB1D69C5B60537C1B992911590BD8F259C9D26D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3F9C675D-7E7A-4AC8-B2E2-695B7BE06A17}"/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="9495" yWindow="-105" windowWidth="29010" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
-  <si>
-    <t>CV_Filename</t>
-  </si>
-  <si>
-    <t>Education Bachelor University</t>
-  </si>
-  <si>
-    <t>Education Bachelor GPA</t>
-  </si>
-  <si>
-    <t>Education Bachelor Major</t>
-  </si>
-  <si>
-    <t>Education Bachelor Graduation Date</t>
-  </si>
-  <si>
-    <t>Education Masters University</t>
-  </si>
-  <si>
-    <t>Education Masters GPA</t>
-  </si>
-  <si>
-    <t>Education Masters Major</t>
-  </si>
-  <si>
-    <t>Education Masters Graduation Date</t>
-  </si>
-  <si>
-    <t>Education PhD University</t>
-  </si>
-  <si>
-    <t>Education PhD GPA</t>
-  </si>
-  <si>
-    <t>Education PhD Major</t>
-  </si>
-  <si>
-    <t>Education PhD Graduation Date</t>
-  </si>
-  <si>
-    <t>Years of Experience</t>
-  </si>
-  <si>
-    <t>Experience Companies</t>
-  </si>
-  <si>
-    <t>Top 5 Responsibilities/Projects</t>
-  </si>
-  <si>
-    <t>Top 5 Courses/Certifications</t>
-  </si>
-  <si>
-    <t>Top 3 Technical Skills</t>
-  </si>
-  <si>
-    <t>Top 3 Soft Skills</t>
-  </si>
-  <si>
-    <t>Current Employment Status</t>
-  </si>
-  <si>
-    <t>Nationality</t>
-  </si>
-  <si>
-    <t>Current Residence</t>
-  </si>
-  <si>
-    <t>Suitable Position</t>
-  </si>
-  <si>
-    <t>Candidate Rating (Out of 10)</t>
-  </si>
-  <si>
-    <t>All_Info_JSON</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="2">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <name val="Calibri"/>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -132,43 +46,93 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -456,112 +420,377 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B1:Z1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="31.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="42.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="22.5703125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="32.140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="33.5703125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="27.42578125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="22" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="23.42578125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="33" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="23.7109375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="18.28515625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="19.7109375" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="29.28515625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="18.7109375" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="37" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="255.7109375" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="23.5703125" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="50.5703125" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="25.85546875" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="17.5703125" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="21.5703125" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="26.42578125" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="255.7109375" bestFit="1" customWidth="1"/>
-  </cols>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Y3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="2:26" x14ac:dyDescent="0.25">
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="F1" s="1" t="s">
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Filename</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Full Name</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Email Address</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Phone Number</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>LinkedIn URL</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Portfolio URLs</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>City</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Country</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Professional Summary</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Education History</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Years of Experience</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Management Level</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Companies</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Job Titles</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Key Responsibilities</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Technical Skills</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Soft Skills</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>Languages</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>Key Projects</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>Certifications</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>Awards</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>Nationality</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>Employment Status</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>Suitable Positions</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Rating</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Ali Abuharb's CV.pdf</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Ali Ibrahim Ali Abuharb</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Ali.i.Abuharb@gmail.com</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>+966541211120</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/ali-abuharb-3b4905153</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>https://github.com/Aillian</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Riyadh</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Saudi Arabia</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Results-driven AI leader and engineer specializing in Generative/Agentic AI and LLMs. Experienced in leading cross-functional teams to deliver production-grade AI systems, product strategy, commercialization, and go-to-market. Skilled in LLM fine-tuning, multi-GPU training, RAG, and building domain-specific conversational agents. Motivated to contribute to national-scale projects.</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Bachelor in Management Information Systems at King Fahd University of Petroleum &amp; Minerals (May, 2020)</t>
+        </is>
+      </c>
+      <c r="K2" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>Senior / Manager</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>IMO, EY, SDM, AlphaMinds, SITE, Dawah Association in Rawdah, Ministry of Interior, Lean</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>AI Consultant (Contract), Assistant Manager, Technology Consulting (Full-Time), AI Consultant (Contract), Founder &amp; CEO (Full-Time), Lead AI Engineer, Data Department (Full-Time), Generative AI Consultant / Developer (Contract), Data Science Expert / Consultant (Contract), Sr. Machine Learning Engineer, Advanced Analytics Department (Full-Time)</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>IMO: Lead AI team, initiatives, and business development, Develop ASR pipelines (preprocessing, diarization, VAD, speaker ID), Design ASR model evaluation pipelines, Develop agentic AI system for board meeting assistance, Oversee deployment and evaluation of audio/ASR solutions; EY: Lead cross-functional teams on AI initiatives and business development, Develop client AI strategies and solutions, Build and deploy production AI products, Design and implement LLM-based projects, Align technical delivery with business objectives; SDM: Lead AI team, projects, and hiring, Define AI strategy, product roadmaps, and KPIs, Lead Arabic-focused LLM design, fine-tuning, and training pipelines, Drive prompt engineering, RAG, deployments, and monitoring, Mentor team and run knowledge transfers; AlphaMinds: Built Hadi, multilingual AI assistant for religious dialogue using fine-tuned LLMs, Led cross-functional teams to design and deploy generative and agentic AI products, Developed domain chatbots (medical, cancer, finance) and telephone AI agents, Built offline self-hosted generative AI platform and multi-agent systems, Created ResumeGPT open-source package for CV extraction; SITE: Led AI team and initiatives, Developed similarity algorithm to match local vulnerabilities with global CVEs, Built ETL pipeline for Saudi News Registry, Developed NER model (GLiNER) for news entity extraction, Built LLM agent to classify Saudi-related news; Dawah Association in Rawdah: Fine-tuned open-source and closed models; used DeepSpeed, FSDP, LoRA, QLoRA, GPTQ, Planned projects (timeline, resources, servers) and generated synthetic Islamic data, Built Islamic QA RAG bot, reducing user search time by 98%, Extracted and cleaned website chat data, Deployed multi-GPU training and quantization strategies; Ministry of Interior: Planned and developed Data Quality Engine using Alteryx, Built ETLs to feed MOI data into the quality engine, Assessed data quality index across MOI sectors, Delivered 12 workshops on Data Quality Maturity Index, Coordinated cross-sector data quality activities; Lean: Led Generative AI &amp; LLMs team and cross-functional resources, Built Sehaty symptom-checker conversational AI and medical knowledge base, Developed medical and clinical chatbots for patients and clinicians, Built DRG engine and data quality engines using Alteryx and Python, Delivered multiple ML, NLP, CV projects and production ETLs/dashboards</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>Generative AI &amp; LLMs (fine-tuning, RAG, prompt engineering), Python (PyTorch, HuggingFace, TensorFlow), Natural Language Processing (NER, ASR, STT, TTS), Deep Learning &amp; Computer Vision, Data Engineering &amp; ETL (Alteryx, SQL, PySpark)</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>Leadership, Communication, Product Management, Project Management, Business Development</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>Arabic (Native), English (Professional / Fluent)</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>Hadi: multilingual AI assistant for inviting non-Muslims to Islam; fine-tuned and deployed with multi-GPU training and quantization., Telephone Customer Service AI Agent: multi-language, Saudi-dialect optimized pipeline (VAD, STT, LLM, TTS)., Offline Generative AI Platform: self-hosted ChatGPT-like platform using Ollama, RAG, LLM tools for private environments., ResumeGPT: open-source Python package using OCR and LLMs to extract structured data from CV PDFs (50+ stars on GitHub)., Sehaty Symptom Checker: medical conversational AI that diagnoses, generates triage reports and integrates with medical knowledge base.</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>Certified Associate: Generative AI LLMs – Nvidia (2024), Large Language Models Bootcamp – Data Science Dojo &amp; University of New Mexico (2024), Advanced Reinforcement Learning – MIT (2023), Nanodegree, Machine Learning – Misk / Udacity (2020), Certified Google Analytics IQ (2019)</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>First place, Smart Transactions Track – KFUPM FinTech Regional Hackathon (2019), Second place, Data Science Track – MIT Health Hackathon (2018), Finalist, Machine Learning Hackathon – Thakaa Center (2020), Multiple hackathon participations and finalist placements (2018–2020), Presented two papers – ISPOR Conference (2023)</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>Saudi</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>Employed</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Head of AI / AI Lead, Senior Machine Learning / LLM Engineer, Generative AI / LLM Architect, AI Product Manager, Generative AI Consultant</t>
+        </is>
+      </c>
+      <c r="Y2" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Ghada Alshabib cv 2023 updated.pdf</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Ghada Alshabib</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>ghadamalshabib@gmail.com</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>+966 56 387 8402</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Riyadh</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Saudi Arabia</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Computer Science graduate with strong mathematics background and a passion for machine learning and data analytics. Experienced in data analysis, data quality (Informatica), visualization (Tableau, Power BI), and data cleansing. Seeking opportunities to apply and grow technical skills.</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>BSc in Computer Science at King Saud University (June, 2022)</t>
+        </is>
+      </c>
+      <c r="K3" t="n">
         <v>4</v>
       </c>
-      <c r="G1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="I1" s="1" t="s">
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>Mid-level (Individual Contributor)</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>Devoteam Middle East, King Abdulaziz City for Science and Technology (KACST)</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>Consultant, Android Development Intern</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>Devoteam Middle East: Analyzed large and complex datasets to identify patterns and insights., Used Informatica for data profiling and to create data quality rules., Built interactive dashboards with Tableau and Power BI., Performed data cleansing: deduplication, filling missing values, correcting errors., Ensured data alignment with business rules and stakeholder requirements.; King Abdulaziz City for Science and Technology (KACST): Designed UI/UX for an Android application for the National Center for Cybersecurity Technology., Collaborated on mobile app development and prototyping., Conducted usability refinements for the app interface.</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Python, SQL, Informatica, Tableau, Power BI</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>Quick learner, Problem solving, Team player, Attention to detail, Communication</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>English (Fluent), Arabic (Native)</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>Multiple online exams composition problem — Graduation project (2022)., Credit card churn predictions — Machine learning project (2021)., Pharmacy management system — Database project (2020)., Internet of Things Security Solutions — Ethics paper (2020)., Android app UI/UX for National Center for Cybersecurity Technology — Internship (2021).</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>DevoGame Cloud Investigation Finalist (2nd Place) — Devoteam (2021)</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>DevoGame Cloud Investigation Finalist (2nd Place) — Devoteam (2021)</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Saudi Arabian</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Employed</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Data Analyst, Business Intelligence Analyst, Data Quality Analyst, Junior Machine Learning Engineer, Data Engineer (entry-level)</t>
+        </is>
+      </c>
+      <c r="Y3" t="n">
         <v>7</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="S1" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="T1" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="U1" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="V1" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="W1" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="X1" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="Y1" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="Z1" s="1" t="s">
-        <v>24</v>
       </c>
     </row>
   </sheetData>
